--- a/psychopy_exp_files/sequences/localizer_conditions_things-meg_mixed_5cat_02.xlsx
+++ b/psychopy_exp_files/sequences/localizer_conditions_things-meg_mixed_5cat_02.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -559,12 +559,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -12919,12 +12919,12 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -13537,12 +13537,12 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -14277,12 +14277,12 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -16192,12 +16192,12 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -16932,12 +16932,12 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -17054,7 +17054,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -17863,12 +17863,12 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -18298,12 +18298,12 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -19595,12 +19595,12 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -19900,12 +19900,12 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -20457,12 +20457,12 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -21205,12 +21205,12 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -21496,7 +21496,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -21510,12 +21510,12 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -22175,7 +22175,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G352" t="n">
@@ -22189,12 +22189,12 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -22366,7 +22366,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G355" t="n">
@@ -22380,12 +22380,12 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -22915,7 +22915,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G364" t="n">
@@ -22929,12 +22929,12 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -24265,7 +24265,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G386" t="n">
@@ -24279,12 +24279,12 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -24467,7 +24467,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -24639,7 +24639,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G392" t="n">
@@ -24653,12 +24653,12 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -25440,7 +25440,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G405" t="n">
@@ -25454,12 +25454,12 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -25570,7 +25570,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G407" t="n">
@@ -25584,12 +25584,12 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -26188,7 +26188,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G417" t="n">
@@ -26202,12 +26202,12 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -26817,7 +26817,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -27355,7 +27355,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G436" t="n">
@@ -27369,12 +27369,12 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
@@ -27729,7 +27729,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G442" t="n">
@@ -27743,12 +27743,12 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -28705,7 +28705,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G458" t="n">
@@ -28719,12 +28719,12 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -29148,7 +29148,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G465" t="n">
@@ -29162,12 +29162,12 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -29758,7 +29758,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G475" t="n">
@@ -29772,12 +29772,12 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -30077,7 +30077,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
@@ -30376,7 +30376,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G485" t="n">
@@ -30390,12 +30390,12 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G507" t="n">
@@ -31740,12 +31740,12 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -32405,7 +32405,7 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G518" t="n">
@@ -32419,12 +32419,12 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
@@ -32588,7 +32588,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G521" t="n">
@@ -32602,12 +32602,12 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G537" t="n">
@@ -33586,7 +33586,7 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G543" t="n">
@@ -33968,12 +33968,12 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G567" t="n">
@@ -35448,12 +35448,12 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G579" t="n">
@@ -36180,12 +36180,12 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K579" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
@@ -36288,7 +36288,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G581" t="n">
@@ -36302,12 +36302,12 @@
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K581" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L581" t="inlineStr">
@@ -36967,7 +36967,7 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G592" t="n">
@@ -36981,12 +36981,12 @@
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K592" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G598" t="n">
@@ -37355,12 +37355,12 @@
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K598" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
@@ -37829,7 +37829,7 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G606" t="n">
@@ -37843,12 +37843,12 @@
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
@@ -38031,7 +38031,7 @@
       </c>
       <c r="K609" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L609" t="inlineStr">
@@ -38691,7 +38691,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G620" t="n">
@@ -38705,12 +38705,12 @@
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K620" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
@@ -38943,7 +38943,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G624" t="n">
@@ -38957,12 +38957,12 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
@@ -39561,7 +39561,7 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G634" t="n">
@@ -39575,12 +39575,12 @@
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K634" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
@@ -40667,7 +40667,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G652" t="n">
@@ -40681,12 +40681,12 @@
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L652" t="inlineStr">
